--- a/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-PR-AuditEvent.xlsx
+++ b/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-PR-AuditEvent.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3507" uniqueCount="603">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3523" uniqueCount="611">
   <si>
     <t>Property</t>
   </si>
@@ -511,6 +511,13 @@
     <t>Meta.security</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>CV</t>
+  </si>
+  <si>
     <t>AuditEvent.meta.tag</t>
   </si>
   <si>
@@ -664,6 +671,9 @@
     <t>Identifier for a family of the event.  For example, a menu item, program, rule, policy, function code, application name or URL. It identifies the performed function.</t>
   </si>
   <si>
+    <t>Codes may be defined very casually in enumerations or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.</t>
+  </si>
+  <si>
     <t>This identifies the performed function. For "Execute" Event Action Code audit records, this identifies the application function performed.</t>
   </si>
   <si>
@@ -764,6 +774,9 @@
   </si>
   <si>
     <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
   </si>
   <si>
     <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
@@ -861,6 +874,10 @@
     <t>The period can be a little arbitrary; where possible, the time should correspond to human assessment of the activity time.</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+per-1:If present, start SHALL have a lower value than end {start.hasValue().not() or end.hasValue().not() or (start &lt;= end)}</t>
+  </si>
+  <si>
     <t>Event.occurred[x]</t>
   </si>
   <si>
@@ -1057,6 +1074,9 @@
     <t>Specification of the participation type the user plays when performing the event.</t>
   </si>
   <si>
+    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
+  </si>
+  <si>
     <t>The Participation type of the agent to the event.</t>
   </si>
   <si>
@@ -1126,6 +1146,10 @@
   </si>
   <si>
     <t>This field ties an audit event to a specific resource or identifier.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -1298,6 +1322,9 @@
   </si>
   <si>
     <t>Where the event occurred.</t>
+  </si>
+  <si>
+    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
   </si>
   <si>
     <t>Event.location</t>
@@ -3663,7 +3690,7 @@
         <v>81</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>79</v>
+        <v>159</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>103</v>
@@ -3672,7 +3699,7 @@
         <v>79</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>79</v>
+        <v>160</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>79</v>
@@ -3689,10 +3716,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3718,13 +3745,13 @@
         <v>151</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3750,13 +3777,13 @@
         <v>79</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>79</v>
@@ -3774,7 +3801,7 @@
         <v>79</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3783,7 +3810,7 @@
         <v>81</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>79</v>
+        <v>159</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>103</v>
@@ -3792,7 +3819,7 @@
         <v>79</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>79</v>
+        <v>160</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>79</v>
@@ -3809,10 +3836,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3838,13 +3865,13 @@
         <v>133</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3894,7 +3921,7 @@
         <v>79</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -3929,10 +3956,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3955,16 +3982,16 @@
         <v>79</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3990,13 +4017,13 @@
         <v>79</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>79</v>
@@ -4014,7 +4041,7 @@
         <v>79</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -4049,14 +4076,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -4075,16 +4102,16 @@
         <v>79</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4134,7 +4161,7 @@
         <v>79</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -4152,7 +4179,7 @@
         <v>79</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>79</v>
@@ -4169,14 +4196,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -4195,16 +4222,16 @@
         <v>79</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4254,7 +4281,7 @@
         <v>79</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -4272,7 +4299,7 @@
         <v>79</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>79</v>
@@ -4289,10 +4316,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4321,7 +4348,7 @@
         <v>113</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>115</v>
@@ -4362,19 +4389,19 @@
         <v>79</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4392,7 +4419,7 @@
         <v>79</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>79</v>
@@ -4409,10 +4436,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4438,16 +4465,16 @@
         <v>112</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="N19" t="s" s="2">
         <v>115</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>79</v>
@@ -4484,19 +4511,19 @@
         <v>79</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4514,7 +4541,7 @@
         <v>79</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>79</v>
@@ -4531,10 +4558,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4560,14 +4587,16 @@
         <v>151</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="N20" s="2"/>
+        <v>209</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>210</v>
+      </c>
       <c r="O20" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>79</v>
@@ -4595,10 +4624,10 @@
         <v>155</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>79</v>
@@ -4616,7 +4645,7 @@
         <v>79</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>91</v>
@@ -4625,25 +4654,25 @@
         <v>91</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>79</v>
+        <v>159</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>79</v>
@@ -4651,10 +4680,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4769,10 +4798,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4889,10 +4918,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4918,23 +4947,23 @@
         <v>133</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="S23" t="s" s="2">
         <v>79</v>
@@ -4976,7 +5005,7 @@
         <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4994,7 +5023,7 @@
         <v>79</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>79</v>
@@ -5011,10 +5040,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5040,13 +5069,13 @@
         <v>105</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -5096,7 +5125,7 @@
         <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -5114,7 +5143,7 @@
         <v>79</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>79</v>
@@ -5131,10 +5160,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5157,24 +5186,24 @@
         <v>92</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="S25" t="s" s="2">
         <v>79</v>
@@ -5216,7 +5245,7 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -5234,7 +5263,7 @@
         <v>79</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>79</v>
@@ -5251,10 +5280,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5280,14 +5309,16 @@
         <v>105</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>244</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="O26" t="s" s="2">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>79</v>
@@ -5336,7 +5367,7 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5354,7 +5385,7 @@
         <v>79</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>79</v>
@@ -5371,10 +5402,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5397,19 +5428,19 @@
         <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>79</v>
@@ -5458,7 +5489,7 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5476,7 +5507,7 @@
         <v>79</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>79</v>
@@ -5493,10 +5524,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5522,14 +5553,16 @@
         <v>151</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>259</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>210</v>
+      </c>
       <c r="O28" t="s" s="2">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>79</v>
@@ -5557,28 +5590,28 @@
         <v>155</v>
       </c>
       <c r="Y28" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="Z28" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AA28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF28" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="Z28" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="AA28" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB28" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD28" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE28" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF28" t="s" s="2">
-        <v>253</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5587,7 +5620,7 @@
         <v>81</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>79</v>
+        <v>159</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>103</v>
@@ -5596,13 +5629,13 @@
         <v>79</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>79</v>
@@ -5613,10 +5646,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5639,17 +5672,17 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>79</v>
@@ -5674,31 +5707,31 @@
         <v>79</v>
       </c>
       <c r="X29" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="Z29" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF29" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="Y29" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="Z29" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="AA29" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB29" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD29" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE29" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF29" t="s" s="2">
-        <v>260</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5716,13 +5749,13 @@
         <v>79</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>79</v>
@@ -5733,10 +5766,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5759,16 +5792,16 @@
         <v>79</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5818,7 +5851,7 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5827,36 +5860,36 @@
         <v>91</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>79</v>
+        <v>159</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>103</v>
+        <v>277</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>278</v>
+        <v>283</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5882,16 +5915,16 @@
         <v>127</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>79</v>
@@ -5940,7 +5973,7 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>91</v>
@@ -5958,27 +5991,27 @@
         <v>79</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>287</v>
+        <v>292</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6001,16 +6034,16 @@
         <v>92</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6036,13 +6069,13 @@
         <v>79</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>79</v>
@@ -6060,7 +6093,7 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -6078,13 +6111,13 @@
         <v>79</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>79</v>
@@ -6095,10 +6128,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6124,12 +6157,14 @@
         <v>105</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="N33" s="2"/>
+        <v>302</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>79</v>
@@ -6178,7 +6213,7 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6196,13 +6231,13 @@
         <v>79</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>79</v>
@@ -6213,10 +6248,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6239,16 +6274,16 @@
         <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6277,28 +6312,28 @@
         <v>155</v>
       </c>
       <c r="Y34" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="Z34" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF34" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="Z34" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="AA34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF34" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6307,40 +6342,40 @@
         <v>81</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>79</v>
+        <v>159</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>312</v>
+        <v>317</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6359,19 +6394,19 @@
         <v>79</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>79</v>
@@ -6420,7 +6455,7 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>91</v>
@@ -6429,36 +6464,36 @@
         <v>81</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>79</v>
+        <v>159</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6573,10 +6608,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6646,16 +6681,16 @@
         <v>79</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="AF37" t="s" s="2">
         <v>119</v>
@@ -6693,14 +6728,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6722,16 +6757,16 @@
         <v>112</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="N38" t="s" s="2">
         <v>115</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>79</v>
@@ -6780,7 +6815,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6798,7 +6833,7 @@
         <v>79</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>79</v>
@@ -6815,10 +6850,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6841,15 +6876,17 @@
         <v>79</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>340</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>341</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>79</v>
@@ -6877,10 +6914,10 @@
         <v>155</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>79</v>
@@ -6898,7 +6935,7 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6907,36 +6944,36 @@
         <v>91</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>79</v>
+        <v>159</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>342</v>
+        <v>348</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6959,19 +6996,19 @@
         <v>79</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>79</v>
@@ -6996,31 +7033,31 @@
         <v>79</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="Z40" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF40" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="AA40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF40" t="s" s="2">
-        <v>343</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -7029,7 +7066,7 @@
         <v>81</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>79</v>
+        <v>159</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>103</v>
@@ -7038,31 +7075,31 @@
         <v>79</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>351</v>
+        <v>357</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7081,19 +7118,19 @@
         <v>92</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>79</v>
@@ -7142,7 +7179,7 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7151,36 +7188,36 @@
         <v>91</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>79</v>
+        <v>159</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>103</v>
+        <v>365</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>363</v>
+        <v>370</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7295,10 +7332,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7415,10 +7452,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7444,13 +7481,13 @@
         <v>105</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7500,7 +7537,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7509,7 +7546,7 @@
         <v>91</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>103</v>
@@ -7518,7 +7555,7 @@
         <v>79</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>79</v>
@@ -7535,10 +7572,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7564,13 +7601,13 @@
         <v>133</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7599,10 +7636,10 @@
         <v>155</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>79</v>
@@ -7620,7 +7657,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7638,7 +7675,7 @@
         <v>79</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>79</v>
@@ -7655,10 +7692,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7681,16 +7718,16 @@
         <v>92</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7740,7 +7777,7 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7749,7 +7786,7 @@
         <v>91</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>79</v>
+        <v>159</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>103</v>
@@ -7758,7 +7795,7 @@
         <v>79</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>79</v>
@@ -7775,10 +7812,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7804,13 +7841,13 @@
         <v>105</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7860,7 +7897,7 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7878,7 +7915,7 @@
         <v>79</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>79</v>
@@ -7895,10 +7932,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7924,14 +7961,16 @@
         <v>105</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>400</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="O48" t="s" s="2">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>79</v>
@@ -7980,7 +8019,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7998,16 +8037,16 @@
         <v>79</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>79</v>
@@ -8015,10 +8054,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8044,14 +8083,16 @@
         <v>105</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>406</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="O49" t="s" s="2">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>79</v>
@@ -8100,7 +8141,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8118,16 +8159,16 @@
         <v>79</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>79</v>
@@ -8135,10 +8176,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8161,19 +8202,19 @@
         <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>79</v>
@@ -8222,7 +8263,7 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>91</v>
@@ -8240,13 +8281,13 @@
         <v>79</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>79</v>
@@ -8257,10 +8298,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8283,15 +8324,17 @@
         <v>79</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="N51" s="2"/>
+        <v>420</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>421</v>
+      </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>79</v>
@@ -8340,7 +8383,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8349,36 +8392,36 @@
         <v>91</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>79</v>
+        <v>159</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>103</v>
+        <v>365</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>418</v>
+        <v>426</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8404,16 +8447,16 @@
         <v>133</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>79</v>
@@ -8462,7 +8505,7 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8480,27 +8523,27 @@
         <v>79</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>426</v>
+        <v>434</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8526,14 +8569,16 @@
         <v>151</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>437</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>210</v>
+      </c>
       <c r="O53" t="s" s="2">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>79</v>
@@ -8561,10 +8606,10 @@
         <v>155</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>79</v>
@@ -8582,7 +8627,7 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8591,7 +8636,7 @@
         <v>91</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>79</v>
+        <v>159</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>103</v>
@@ -8600,13 +8645,13 @@
         <v>79</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>79</v>
@@ -8617,10 +8662,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8643,13 +8688,13 @@
         <v>79</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8700,7 +8745,7 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8709,7 +8754,7 @@
         <v>91</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>79</v>
+        <v>159</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>103</v>
@@ -8718,13 +8763,13 @@
         <v>79</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>79</v>
@@ -8735,10 +8780,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8853,10 +8898,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8926,16 +8971,16 @@
         <v>79</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="AC56" t="s" s="2">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="AD56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="AF56" t="s" s="2">
         <v>119</v>
@@ -8973,14 +9018,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -9002,16 +9047,16 @@
         <v>112</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>115</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>79</v>
@@ -9060,7 +9105,7 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9078,7 +9123,7 @@
         <v>79</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>79</v>
@@ -9095,10 +9140,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9124,16 +9169,16 @@
         <v>105</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>79</v>
@@ -9182,7 +9227,7 @@
         <v>79</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9200,16 +9245,16 @@
         <v>79</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>79</v>
@@ -9217,10 +9262,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9243,17 +9288,17 @@
         <v>79</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>79</v>
@@ -9278,13 +9323,13 @@
         <v>79</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>79</v>
@@ -9302,7 +9347,7 @@
         <v>79</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9320,13 +9365,13 @@
         <v>79</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>79</v>
@@ -9337,10 +9382,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9363,16 +9408,16 @@
         <v>79</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9401,10 +9446,10 @@
         <v>155</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>79</v>
@@ -9422,7 +9467,7 @@
         <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9431,7 +9476,7 @@
         <v>81</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>79</v>
+        <v>159</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>103</v>
@@ -9440,16 +9485,16 @@
         <v>79</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>79</v>
@@ -9457,10 +9502,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9483,19 +9528,19 @@
         <v>79</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>79</v>
@@ -9544,7 +9589,7 @@
         <v>79</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>91</v>
@@ -9553,7 +9598,7 @@
         <v>91</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>79</v>
+        <v>159</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>103</v>
@@ -9562,13 +9607,13 @@
         <v>79</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>79</v>
@@ -9579,10 +9624,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9697,10 +9742,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9770,16 +9815,16 @@
         <v>79</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="AC63" t="s" s="2">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="AD63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="AF63" t="s" s="2">
         <v>119</v>
@@ -9817,14 +9862,14 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -9846,16 +9891,16 @@
         <v>112</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="N64" t="s" s="2">
         <v>115</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>79</v>
@@ -9904,7 +9949,7 @@
         <v>79</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9922,7 +9967,7 @@
         <v>79</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>79</v>
@@ -9939,10 +9984,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9968,21 +10013,23 @@
         <v>105</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="N65" s="2"/>
+        <v>484</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="O65" t="s" s="2">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q65" s="2"/>
       <c r="R65" t="s" s="2">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="S65" t="s" s="2">
         <v>79</v>
@@ -10024,7 +10071,7 @@
         <v>79</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10042,13 +10089,13 @@
         <v>79</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>79</v>
@@ -10059,14 +10106,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -10085,17 +10132,19 @@
         <v>92</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="N66" s="2"/>
+        <v>493</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>421</v>
+      </c>
       <c r="O66" t="s" s="2">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>79</v>
@@ -10144,7 +10193,7 @@
         <v>79</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>91</v>
@@ -10153,22 +10202,22 @@
         <v>91</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>79</v>
+        <v>159</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>103</v>
+        <v>365</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>79</v>
@@ -10179,10 +10228,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>488</v>
+        <v>496</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>488</v>
+        <v>496</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10297,10 +10346,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10417,10 +10466,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10446,13 +10495,13 @@
         <v>105</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10502,7 +10551,7 @@
         <v>79</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10511,7 +10560,7 @@
         <v>91</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>103</v>
@@ -10520,7 +10569,7 @@
         <v>79</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>79</v>
@@ -10537,10 +10586,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>491</v>
+        <v>499</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>491</v>
+        <v>499</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10566,13 +10615,13 @@
         <v>133</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10601,10 +10650,10 @@
         <v>155</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>79</v>
@@ -10622,7 +10671,7 @@
         <v>79</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10640,7 +10689,7 @@
         <v>79</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>79</v>
@@ -10657,10 +10706,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>492</v>
+        <v>500</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>492</v>
+        <v>500</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10683,16 +10732,16 @@
         <v>92</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10742,7 +10791,7 @@
         <v>79</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10751,7 +10800,7 @@
         <v>91</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>79</v>
+        <v>159</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>103</v>
@@ -10760,7 +10809,7 @@
         <v>79</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>79</v>
@@ -10777,10 +10826,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10806,13 +10855,13 @@
         <v>105</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10862,7 +10911,7 @@
         <v>79</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10880,7 +10929,7 @@
         <v>79</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>79</v>
@@ -10897,10 +10946,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10926,14 +10975,16 @@
         <v>151</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="N73" s="2"/>
+        <v>505</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>210</v>
+      </c>
       <c r="O73" t="s" s="2">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>79</v>
@@ -10961,10 +11012,10 @@
         <v>155</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>79</v>
@@ -10982,7 +11033,7 @@
         <v>79</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -10991,7 +11042,7 @@
         <v>81</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>79</v>
+        <v>159</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>103</v>
@@ -11000,13 +11051,13 @@
         <v>79</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>79</v>
@@ -11017,14 +11068,14 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -11043,19 +11094,19 @@
         <v>79</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>507</v>
+        <v>515</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>79</v>
@@ -11104,7 +11155,7 @@
         <v>79</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11113,36 +11164,36 @@
         <v>81</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>79</v>
+        <v>159</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>513</v>
+        <v>521</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11257,10 +11308,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11330,16 +11381,16 @@
         <v>79</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="AC76" t="s" s="2">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="AD76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="AF76" t="s" s="2">
         <v>119</v>
@@ -11377,14 +11428,14 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -11406,16 +11457,16 @@
         <v>112</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="N77" t="s" s="2">
         <v>115</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>79</v>
@@ -11464,7 +11515,7 @@
         <v>79</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11482,7 +11533,7 @@
         <v>79</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>79</v>
@@ -11499,10 +11550,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11525,15 +11576,17 @@
         <v>92</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="N78" s="2"/>
+        <v>528</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>421</v>
+      </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>79</v>
@@ -11582,7 +11635,7 @@
         <v>79</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11591,36 +11644,36 @@
         <v>91</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>79</v>
+        <v>159</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>103</v>
+        <v>365</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>522</v>
+        <v>530</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11646,16 +11699,16 @@
         <v>151</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>526</v>
+        <v>534</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>79</v>
@@ -11683,10 +11736,10 @@
         <v>155</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>79</v>
@@ -11704,7 +11757,7 @@
         <v>79</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11713,7 +11766,7 @@
         <v>91</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>79</v>
+        <v>159</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>103</v>
@@ -11722,27 +11775,27 @@
         <v>79</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>530</v>
+        <v>538</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>531</v>
+        <v>539</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>533</v>
+        <v>541</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11768,14 +11821,16 @@
         <v>151</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="N80" s="2"/>
+        <v>544</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>210</v>
+      </c>
       <c r="O80" t="s" s="2">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>79</v>
@@ -11803,10 +11858,10 @@
         <v>155</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>539</v>
+        <v>547</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>79</v>
@@ -11824,7 +11879,7 @@
         <v>79</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -11833,7 +11888,7 @@
         <v>91</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>79</v>
+        <v>159</v>
       </c>
       <c r="AJ80" t="s" s="2">
         <v>103</v>
@@ -11842,16 +11897,16 @@
         <v>79</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>543</v>
+        <v>551</v>
       </c>
       <c r="AP80" t="s" s="2">
         <v>79</v>
@@ -11859,10 +11914,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>544</v>
+        <v>552</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>544</v>
+        <v>552</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11888,16 +11943,16 @@
         <v>151</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>545</v>
+        <v>553</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>546</v>
+        <v>554</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>547</v>
+        <v>555</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>548</v>
+        <v>556</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>79</v>
@@ -11925,10 +11980,10 @@
         <v>155</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>546</v>
+        <v>554</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>549</v>
+        <v>557</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>79</v>
@@ -11946,7 +12001,7 @@
         <v>79</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>544</v>
+        <v>552</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -11955,7 +12010,7 @@
         <v>91</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>79</v>
+        <v>159</v>
       </c>
       <c r="AJ81" t="s" s="2">
         <v>103</v>
@@ -11964,27 +12019,27 @@
         <v>79</v>
       </c>
       <c r="AL81" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="AN81" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="AM81" t="s" s="2">
+      <c r="AO81" t="s" s="2">
         <v>551</v>
       </c>
-      <c r="AN81" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="AO81" t="s" s="2">
-        <v>543</v>
-      </c>
       <c r="AP81" t="s" s="2">
-        <v>552</v>
+        <v>560</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12010,16 +12065,16 @@
         <v>151</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>554</v>
+        <v>562</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>555</v>
+        <v>563</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>556</v>
+        <v>564</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>557</v>
+        <v>565</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>79</v>
@@ -12068,7 +12123,7 @@
         <v>79</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12077,7 +12132,7 @@
         <v>81</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>79</v>
+        <v>159</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>103</v>
@@ -12086,13 +12141,13 @@
         <v>79</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>559</v>
+        <v>567</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>79</v>
@@ -12103,10 +12158,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>560</v>
+        <v>568</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>560</v>
+        <v>568</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12132,16 +12187,16 @@
         <v>105</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>561</v>
+        <v>569</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>562</v>
+        <v>570</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>563</v>
+        <v>571</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>79</v>
@@ -12190,7 +12245,7 @@
         <v>79</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>560</v>
+        <v>568</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12199,7 +12254,7 @@
         <v>91</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>565</v>
+        <v>573</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>103</v>
@@ -12208,16 +12263,16 @@
         <v>79</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>566</v>
+        <v>574</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>79</v>
@@ -12225,10 +12280,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>569</v>
+        <v>577</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>569</v>
+        <v>577</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12254,14 +12309,16 @@
         <v>105</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>570</v>
+        <v>578</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="N84" s="2"/>
+        <v>579</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="O84" t="s" s="2">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>79</v>
@@ -12310,7 +12367,7 @@
         <v>79</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>569</v>
+        <v>577</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12328,13 +12385,13 @@
         <v>79</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>572</v>
+        <v>580</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>79</v>
@@ -12345,10 +12402,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12371,19 +12428,19 @@
         <v>92</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>575</v>
+        <v>583</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>576</v>
+        <v>584</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>577</v>
+        <v>585</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>578</v>
+        <v>586</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>579</v>
+        <v>587</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>79</v>
@@ -12432,7 +12489,7 @@
         <v>79</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12441,7 +12498,7 @@
         <v>91</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>565</v>
+        <v>573</v>
       </c>
       <c r="AJ85" t="s" s="2">
         <v>103</v>
@@ -12450,13 +12507,13 @@
         <v>79</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>580</v>
+        <v>588</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>581</v>
+        <v>589</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>79</v>
@@ -12467,10 +12524,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>582</v>
+        <v>590</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>582</v>
+        <v>590</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12493,17 +12550,17 @@
         <v>79</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>583</v>
+        <v>591</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>584</v>
+        <v>592</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" t="s" s="2">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>79</v>
@@ -12552,7 +12609,7 @@
         <v>79</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>582</v>
+        <v>590</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12561,7 +12618,7 @@
         <v>81</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>79</v>
+        <v>159</v>
       </c>
       <c r="AJ86" t="s" s="2">
         <v>103</v>
@@ -12570,13 +12627,13 @@
         <v>79</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>587</v>
+        <v>595</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>79</v>
@@ -12587,10 +12644,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>588</v>
+        <v>596</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>588</v>
+        <v>596</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12705,10 +12762,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12778,16 +12835,16 @@
         <v>79</v>
       </c>
       <c r="AB88" t="s" s="2">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="AC88" t="s" s="2">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="AD88" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE88" t="s" s="2">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="AF88" t="s" s="2">
         <v>119</v>
@@ -12825,14 +12882,14 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>590</v>
+        <v>598</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>590</v>
+        <v>598</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -12854,16 +12911,16 @@
         <v>112</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="N89" t="s" s="2">
         <v>115</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>79</v>
@@ -12912,7 +12969,7 @@
         <v>79</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -12930,7 +12987,7 @@
         <v>79</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>79</v>
@@ -12947,10 +13004,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>591</v>
+        <v>599</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>591</v>
+        <v>599</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12976,12 +13033,14 @@
         <v>105</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>592</v>
+        <v>600</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="N90" s="2"/>
+        <v>601</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>79</v>
@@ -13030,7 +13089,7 @@
         <v>79</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>591</v>
+        <v>599</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>91</v>
@@ -13048,13 +13107,13 @@
         <v>79</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>594</v>
+        <v>602</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>79</v>
@@ -13065,10 +13124,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>595</v>
+        <v>603</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>595</v>
+        <v>603</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13091,19 +13150,19 @@
         <v>79</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>596</v>
+        <v>604</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>597</v>
+        <v>605</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>598</v>
+        <v>606</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>600</v>
+        <v>608</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>79</v>
@@ -13152,7 +13211,7 @@
         <v>79</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>595</v>
+        <v>603</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>91</v>
@@ -13161,7 +13220,7 @@
         <v>91</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>79</v>
+        <v>159</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>103</v>
@@ -13170,13 +13229,13 @@
         <v>79</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>602</v>
+        <v>610</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>79</v>

--- a/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-PR-AuditEvent.xlsx
+++ b/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-PR-AuditEvent.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3523" uniqueCount="611">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3507" uniqueCount="603">
   <si>
     <t>Property</t>
   </si>
@@ -511,13 +511,6 @@
     <t>Meta.security</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>CV</t>
-  </si>
-  <si>
     <t>AuditEvent.meta.tag</t>
   </si>
   <si>
@@ -671,9 +664,6 @@
     <t>Identifier for a family of the event.  For example, a menu item, program, rule, policy, function code, application name or URL. It identifies the performed function.</t>
   </si>
   <si>
-    <t>Codes may be defined very casually in enumerations or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.</t>
-  </si>
-  <si>
     <t>This identifies the performed function. For "Execute" Event Action Code audit records, this identifies the application function performed.</t>
   </si>
   <si>
@@ -774,9 +764,6 @@
   </si>
   <si>
     <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
   </si>
   <si>
     <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
@@ -874,10 +861,6 @@
     <t>The period can be a little arbitrary; where possible, the time should correspond to human assessment of the activity time.</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-per-1:If present, start SHALL have a lower value than end {start.hasValue().not() or end.hasValue().not() or (start &lt;= end)}</t>
-  </si>
-  <si>
     <t>Event.occurred[x]</t>
   </si>
   <si>
@@ -1074,9 +1057,6 @@
     <t>Specification of the participation type the user plays when performing the event.</t>
   </si>
   <si>
-    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
-  </si>
-  <si>
     <t>The Participation type of the agent to the event.</t>
   </si>
   <si>
@@ -1146,10 +1126,6 @@
   </si>
   <si>
     <t>This field ties an audit event to a specific resource or identifier.</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -1322,9 +1298,6 @@
   </si>
   <si>
     <t>Where the event occurred.</t>
-  </si>
-  <si>
-    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
   </si>
   <si>
     <t>Event.location</t>
@@ -3690,7 +3663,7 @@
         <v>81</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>159</v>
+        <v>79</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>103</v>
@@ -3699,7 +3672,7 @@
         <v>79</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>160</v>
+        <v>79</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>79</v>
@@ -3716,10 +3689,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3745,13 +3718,13 @@
         <v>151</v>
       </c>
       <c r="L13" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="M13" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="N13" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3777,31 +3750,31 @@
         <v>79</v>
       </c>
       <c r="X13" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="Z13" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="Y13" t="s" s="2">
+      <c r="AA13" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF13" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="AA13" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3810,7 +3783,7 @@
         <v>81</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>159</v>
+        <v>79</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>103</v>
@@ -3819,7 +3792,7 @@
         <v>79</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>160</v>
+        <v>79</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>79</v>
@@ -3836,10 +3809,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3865,13 +3838,13 @@
         <v>133</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="M14" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="N14" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>172</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3921,7 +3894,7 @@
         <v>79</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -3956,10 +3929,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3982,16 +3955,16 @@
         <v>79</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>178</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -4017,31 +3990,31 @@
         <v>79</v>
       </c>
       <c r="X15" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="Z15" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="Y15" t="s" s="2">
+      <c r="AA15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF15" t="s" s="2">
         <v>180</v>
-      </c>
-      <c r="Z15" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>182</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -4076,14 +4049,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -4102,16 +4075,16 @@
         <v>79</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>188</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4161,7 +4134,7 @@
         <v>79</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -4179,7 +4152,7 @@
         <v>79</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>79</v>
@@ -4196,14 +4169,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -4222,16 +4195,16 @@
         <v>79</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4281,7 +4254,7 @@
         <v>79</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -4299,7 +4272,7 @@
         <v>79</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>79</v>
@@ -4316,10 +4289,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4348,7 +4321,7 @@
         <v>113</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>115</v>
@@ -4389,19 +4362,19 @@
         <v>79</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>118</v>
+        <v>79</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4419,7 +4392,7 @@
         <v>79</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>79</v>
@@ -4436,10 +4409,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4465,16 +4438,16 @@
         <v>112</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="N19" t="s" s="2">
         <v>115</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>79</v>
@@ -4511,19 +4484,19 @@
         <v>79</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>118</v>
+        <v>79</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4541,7 +4514,7 @@
         <v>79</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>79</v>
@@ -4558,10 +4531,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4587,16 +4560,14 @@
         <v>151</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>211</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>79</v>
@@ -4624,10 +4595,10 @@
         <v>155</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>79</v>
@@ -4645,7 +4616,7 @@
         <v>79</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>91</v>
@@ -4654,25 +4625,25 @@
         <v>91</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>159</v>
+        <v>79</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="AM20" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AN20" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="AL20" t="s" s="2">
+      <c r="AO20" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="AM20" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>79</v>
@@ -4680,10 +4651,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4798,10 +4769,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4918,10 +4889,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4947,23 +4918,23 @@
         <v>133</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="M23" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="O23" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="S23" t="s" s="2">
         <v>79</v>
@@ -5005,7 +4976,7 @@
         <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -5023,7 +4994,7 @@
         <v>79</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>79</v>
@@ -5040,10 +5011,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5069,13 +5040,13 @@
         <v>105</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -5125,7 +5096,7 @@
         <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -5143,7 +5114,7 @@
         <v>79</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>79</v>
@@ -5160,10 +5131,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5186,24 +5157,24 @@
         <v>92</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="S25" t="s" s="2">
         <v>79</v>
@@ -5245,7 +5216,7 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -5263,7 +5234,7 @@
         <v>79</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>79</v>
@@ -5280,10 +5251,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5309,16 +5280,14 @@
         <v>105</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>245</v>
-      </c>
+        <v>241</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>79</v>
@@ -5367,7 +5336,7 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5385,7 +5354,7 @@
         <v>79</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>79</v>
@@ -5402,10 +5371,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5428,19 +5397,19 @@
         <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="O27" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="L27" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>254</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>79</v>
@@ -5489,7 +5458,7 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5507,7 +5476,7 @@
         <v>79</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>79</v>
@@ -5524,10 +5493,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5553,16 +5522,14 @@
         <v>151</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>210</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>79</v>
@@ -5590,10 +5557,10 @@
         <v>155</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>79</v>
@@ -5611,7 +5578,7 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5620,7 +5587,7 @@
         <v>81</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>159</v>
+        <v>79</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>103</v>
@@ -5629,13 +5596,13 @@
         <v>79</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>79</v>
@@ -5646,10 +5613,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5672,17 +5639,17 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>79</v>
@@ -5707,13 +5674,13 @@
         <v>79</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>79</v>
@@ -5731,7 +5698,7 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5749,13 +5716,13 @@
         <v>79</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>79</v>
@@ -5766,10 +5733,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5792,16 +5759,16 @@
         <v>79</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5851,7 +5818,7 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5860,36 +5827,36 @@
         <v>91</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>159</v>
+        <v>79</v>
       </c>
       <c r="AJ30" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK30" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="AN30" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AO30" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="AK30" t="s" s="2">
+      <c r="AP30" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="AL30" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="AP30" t="s" s="2">
-        <v>283</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5915,16 +5882,16 @@
         <v>127</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>79</v>
@@ -5973,7 +5940,7 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>91</v>
@@ -5991,27 +5958,27 @@
         <v>79</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6034,16 +6001,16 @@
         <v>92</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6069,13 +6036,13 @@
         <v>79</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>79</v>
@@ -6093,7 +6060,7 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -6111,13 +6078,13 @@
         <v>79</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>79</v>
@@ -6128,10 +6095,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6157,14 +6124,12 @@
         <v>105</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>245</v>
-      </c>
+        <v>297</v>
+      </c>
+      <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>79</v>
@@ -6213,7 +6178,7 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6231,13 +6196,13 @@
         <v>79</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>79</v>
@@ -6248,10 +6213,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6274,16 +6239,16 @@
         <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6312,10 +6277,10 @@
         <v>155</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>79</v>
@@ -6333,7 +6298,7 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6342,40 +6307,40 @@
         <v>81</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>159</v>
+        <v>79</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AN34" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AO34" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="AP34" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="AL34" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="AP34" t="s" s="2">
-        <v>317</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6394,19 +6359,19 @@
         <v>79</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>79</v>
@@ -6455,7 +6420,7 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>91</v>
@@ -6464,36 +6429,36 @@
         <v>81</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>159</v>
+        <v>79</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="AN35" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="AO35" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="AP35" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="AL35" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="AP35" t="s" s="2">
-        <v>330</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6608,10 +6573,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6681,16 +6646,16 @@
         <v>79</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>118</v>
+        <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
         <v>119</v>
@@ -6728,14 +6693,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6757,16 +6722,16 @@
         <v>112</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="N38" t="s" s="2">
         <v>115</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>79</v>
@@ -6815,7 +6780,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6833,7 +6798,7 @@
         <v>79</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>79</v>
@@ -6850,10 +6815,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6876,17 +6841,15 @@
         <v>79</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>341</v>
-      </c>
+        <v>335</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>79</v>
@@ -6914,10 +6877,10 @@
         <v>155</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>79</v>
@@ -6935,7 +6898,7 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6944,36 +6907,36 @@
         <v>91</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>159</v>
+        <v>79</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>348</v>
+        <v>342</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6996,19 +6959,19 @@
         <v>79</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>79</v>
@@ -7033,13 +6996,13 @@
         <v>79</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>79</v>
@@ -7057,7 +7020,7 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -7066,7 +7029,7 @@
         <v>81</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>159</v>
+        <v>79</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>103</v>
@@ -7075,31 +7038,31 @@
         <v>79</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>357</v>
+        <v>351</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7118,19 +7081,19 @@
         <v>92</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>79</v>
@@ -7179,7 +7142,7 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7188,36 +7151,36 @@
         <v>91</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>159</v>
+        <v>79</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>365</v>
+        <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>370</v>
+        <v>363</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7332,10 +7295,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7452,10 +7415,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7481,13 +7444,13 @@
         <v>105</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7537,7 +7500,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7546,7 +7509,7 @@
         <v>91</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>103</v>
@@ -7555,7 +7518,7 @@
         <v>79</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>79</v>
@@ -7572,10 +7535,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7601,13 +7564,13 @@
         <v>133</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7636,10 +7599,10 @@
         <v>155</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>79</v>
@@ -7657,7 +7620,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7675,7 +7638,7 @@
         <v>79</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>79</v>
@@ -7692,10 +7655,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7718,16 +7681,16 @@
         <v>92</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7777,7 +7740,7 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7786,7 +7749,7 @@
         <v>91</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>159</v>
+        <v>79</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>103</v>
@@ -7795,7 +7758,7 @@
         <v>79</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>79</v>
@@ -7812,10 +7775,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7841,13 +7804,13 @@
         <v>105</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7897,7 +7860,7 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7915,7 +7878,7 @@
         <v>79</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>79</v>
@@ -7932,10 +7895,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7961,16 +7924,14 @@
         <v>105</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>245</v>
-      </c>
+        <v>393</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>79</v>
@@ -8019,7 +7980,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8037,16 +7998,16 @@
         <v>79</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>79</v>
@@ -8054,10 +8015,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8083,16 +8044,14 @@
         <v>105</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>245</v>
-      </c>
+        <v>399</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>79</v>
@@ -8141,7 +8100,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8159,16 +8118,16 @@
         <v>79</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>79</v>
@@ -8176,10 +8135,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8202,19 +8161,19 @@
         <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>79</v>
@@ -8263,7 +8222,7 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>91</v>
@@ -8281,13 +8240,13 @@
         <v>79</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>79</v>
@@ -8298,10 +8257,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8324,17 +8283,15 @@
         <v>79</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>421</v>
-      </c>
+        <v>413</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>79</v>
@@ -8383,45 +8340,45 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN51" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AO51" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="AG51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH51" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI51" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="AJ51" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="AK51" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="AL51" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>425</v>
-      </c>
       <c r="AP51" t="s" s="2">
-        <v>426</v>
+        <v>418</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8447,16 +8404,16 @@
         <v>133</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>79</v>
@@ -8505,7 +8462,7 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8523,27 +8480,27 @@
         <v>79</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>434</v>
+        <v>426</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8569,16 +8526,14 @@
         <v>151</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>210</v>
-      </c>
+        <v>429</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>79</v>
@@ -8606,10 +8561,10 @@
         <v>155</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>439</v>
+        <v>431</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>79</v>
@@ -8627,7 +8582,7 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8636,7 +8591,7 @@
         <v>91</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>159</v>
+        <v>79</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>103</v>
@@ -8645,13 +8600,13 @@
         <v>79</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>79</v>
@@ -8662,10 +8617,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>443</v>
+        <v>435</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>443</v>
+        <v>435</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8688,13 +8643,13 @@
         <v>79</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8745,7 +8700,7 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>443</v>
+        <v>435</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8754,7 +8709,7 @@
         <v>91</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>159</v>
+        <v>79</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>103</v>
@@ -8763,13 +8718,13 @@
         <v>79</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>79</v>
@@ -8780,10 +8735,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8898,10 +8853,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8971,16 +8926,16 @@
         <v>79</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AC56" t="s" s="2">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="AD56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>118</v>
+        <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
         <v>119</v>
@@ -9018,14 +8973,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -9047,16 +9002,16 @@
         <v>112</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>115</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>79</v>
@@ -9105,7 +9060,7 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9123,7 +9078,7 @@
         <v>79</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>79</v>
@@ -9140,10 +9095,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>450</v>
+        <v>442</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>450</v>
+        <v>442</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9169,16 +9124,16 @@
         <v>105</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>451</v>
+        <v>443</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>452</v>
+        <v>444</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>453</v>
+        <v>445</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>79</v>
@@ -9227,7 +9182,7 @@
         <v>79</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>450</v>
+        <v>442</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9245,16 +9200,16 @@
         <v>79</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>457</v>
+        <v>449</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>79</v>
@@ -9262,10 +9217,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9288,17 +9243,17 @@
         <v>79</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>79</v>
@@ -9323,13 +9278,13 @@
         <v>79</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>462</v>
+        <v>454</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>79</v>
@@ -9347,7 +9302,7 @@
         <v>79</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9365,13 +9320,13 @@
         <v>79</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>79</v>
@@ -9382,10 +9337,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9408,16 +9363,16 @@
         <v>79</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9446,10 +9401,10 @@
         <v>155</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>79</v>
@@ -9467,7 +9422,7 @@
         <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9476,7 +9431,7 @@
         <v>81</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>159</v>
+        <v>79</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>103</v>
@@ -9485,16 +9440,16 @@
         <v>79</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>79</v>
@@ -9502,10 +9457,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9528,19 +9483,19 @@
         <v>79</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>79</v>
@@ -9589,7 +9544,7 @@
         <v>79</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>91</v>
@@ -9598,7 +9553,7 @@
         <v>91</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>159</v>
+        <v>79</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>103</v>
@@ -9607,13 +9562,13 @@
         <v>79</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>478</v>
+        <v>470</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>79</v>
@@ -9624,10 +9579,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9742,10 +9697,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>480</v>
+        <v>472</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>480</v>
+        <v>472</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9815,16 +9770,16 @@
         <v>79</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AC63" t="s" s="2">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="AD63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>118</v>
+        <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
         <v>119</v>
@@ -9862,14 +9817,14 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -9891,16 +9846,16 @@
         <v>112</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="N64" t="s" s="2">
         <v>115</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>79</v>
@@ -9949,7 +9904,7 @@
         <v>79</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9967,7 +9922,7 @@
         <v>79</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>79</v>
@@ -9984,10 +9939,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10013,23 +9968,21 @@
         <v>105</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>245</v>
-      </c>
+        <v>476</v>
+      </c>
+      <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>485</v>
+        <v>477</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q65" s="2"/>
       <c r="R65" t="s" s="2">
-        <v>486</v>
+        <v>478</v>
       </c>
       <c r="S65" t="s" s="2">
         <v>79</v>
@@ -10071,7 +10024,7 @@
         <v>79</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10089,13 +10042,13 @@
         <v>79</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>487</v>
+        <v>479</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>478</v>
+        <v>470</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>79</v>
@@ -10106,14 +10059,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -10132,19 +10085,17 @@
         <v>92</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>492</v>
+        <v>484</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>421</v>
-      </c>
+        <v>485</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>79</v>
@@ -10193,7 +10144,7 @@
         <v>79</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>91</v>
@@ -10202,22 +10153,22 @@
         <v>91</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>159</v>
+        <v>79</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>365</v>
+        <v>103</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>495</v>
+        <v>487</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>478</v>
+        <v>470</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>79</v>
@@ -10228,10 +10179,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>496</v>
+        <v>488</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>496</v>
+        <v>488</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10346,10 +10297,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>497</v>
+        <v>489</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>497</v>
+        <v>489</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10466,10 +10417,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>498</v>
+        <v>490</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>498</v>
+        <v>490</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10495,13 +10446,13 @@
         <v>105</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10551,7 +10502,7 @@
         <v>79</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10560,7 +10511,7 @@
         <v>91</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>103</v>
@@ -10569,7 +10520,7 @@
         <v>79</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>79</v>
@@ -10586,10 +10537,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10615,13 +10566,13 @@
         <v>133</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10650,10 +10601,10 @@
         <v>155</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>79</v>
@@ -10671,7 +10622,7 @@
         <v>79</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10689,7 +10640,7 @@
         <v>79</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>79</v>
@@ -10706,10 +10657,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>500</v>
+        <v>492</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>500</v>
+        <v>492</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10732,16 +10683,16 @@
         <v>92</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>501</v>
+        <v>493</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10791,7 +10742,7 @@
         <v>79</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10800,7 +10751,7 @@
         <v>91</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>159</v>
+        <v>79</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>103</v>
@@ -10809,7 +10760,7 @@
         <v>79</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>79</v>
@@ -10826,10 +10777,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>502</v>
+        <v>494</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>502</v>
+        <v>494</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10855,13 +10806,13 @@
         <v>105</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10911,7 +10862,7 @@
         <v>79</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10929,7 +10880,7 @@
         <v>79</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>79</v>
@@ -10946,10 +10897,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>503</v>
+        <v>495</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>503</v>
+        <v>495</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10975,16 +10926,14 @@
         <v>151</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>504</v>
+        <v>496</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>210</v>
-      </c>
+        <v>497</v>
+      </c>
+      <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
-        <v>506</v>
+        <v>498</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>79</v>
@@ -11012,10 +10961,10 @@
         <v>155</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>508</v>
+        <v>500</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>79</v>
@@ -11033,7 +10982,7 @@
         <v>79</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>503</v>
+        <v>495</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11042,7 +10991,7 @@
         <v>81</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>159</v>
+        <v>79</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>103</v>
@@ -11051,13 +11000,13 @@
         <v>79</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>509</v>
+        <v>501</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>510</v>
+        <v>502</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>478</v>
+        <v>470</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>79</v>
@@ -11068,14 +11017,14 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>511</v>
+        <v>503</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>511</v>
+        <v>503</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>512</v>
+        <v>504</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -11094,19 +11043,19 @@
         <v>79</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>513</v>
+        <v>505</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>515</v>
+        <v>507</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>516</v>
+        <v>508</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>79</v>
@@ -11155,7 +11104,7 @@
         <v>79</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>511</v>
+        <v>503</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11164,36 +11113,36 @@
         <v>81</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>159</v>
+        <v>79</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>517</v>
+        <v>509</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>518</v>
+        <v>510</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>519</v>
+        <v>511</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>520</v>
+        <v>512</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>521</v>
+        <v>513</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>522</v>
+        <v>514</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>522</v>
+        <v>514</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11308,10 +11257,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>523</v>
+        <v>515</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>523</v>
+        <v>515</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11381,16 +11330,16 @@
         <v>79</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AC76" t="s" s="2">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="AD76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>118</v>
+        <v>79</v>
       </c>
       <c r="AF76" t="s" s="2">
         <v>119</v>
@@ -11428,14 +11377,14 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -11457,16 +11406,16 @@
         <v>112</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="N77" t="s" s="2">
         <v>115</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>79</v>
@@ -11515,7 +11464,7 @@
         <v>79</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11533,7 +11482,7 @@
         <v>79</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>79</v>
@@ -11550,10 +11499,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11576,17 +11525,15 @@
         <v>92</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>526</v>
+        <v>518</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>421</v>
-      </c>
+        <v>520</v>
+      </c>
+      <c r="N78" s="2"/>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>79</v>
@@ -11635,7 +11582,7 @@
         <v>79</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11644,36 +11591,36 @@
         <v>91</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>159</v>
+        <v>79</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>365</v>
+        <v>103</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>529</v>
+        <v>521</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>530</v>
+        <v>522</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11699,16 +11646,16 @@
         <v>151</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>532</v>
+        <v>524</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>534</v>
+        <v>526</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>535</v>
+        <v>527</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>79</v>
@@ -11736,10 +11683,10 @@
         <v>155</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>537</v>
+        <v>529</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>79</v>
@@ -11757,7 +11704,7 @@
         <v>79</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11766,7 +11713,7 @@
         <v>91</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>159</v>
+        <v>79</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>103</v>
@@ -11775,27 +11722,27 @@
         <v>79</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>538</v>
+        <v>530</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>541</v>
+        <v>533</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11821,16 +11768,14 @@
         <v>151</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>210</v>
-      </c>
+        <v>536</v>
+      </c>
+      <c r="N80" s="2"/>
       <c r="O80" t="s" s="2">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>79</v>
@@ -11858,10 +11803,10 @@
         <v>155</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>547</v>
+        <v>539</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>79</v>
@@ -11879,7 +11824,7 @@
         <v>79</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -11888,7 +11833,7 @@
         <v>91</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>159</v>
+        <v>79</v>
       </c>
       <c r="AJ80" t="s" s="2">
         <v>103</v>
@@ -11897,16 +11842,16 @@
         <v>79</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>548</v>
+        <v>540</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>549</v>
+        <v>541</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>550</v>
+        <v>542</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>551</v>
+        <v>543</v>
       </c>
       <c r="AP80" t="s" s="2">
         <v>79</v>
@@ -11914,10 +11859,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>552</v>
+        <v>544</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>552</v>
+        <v>544</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11943,16 +11888,16 @@
         <v>151</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>553</v>
+        <v>545</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>554</v>
+        <v>546</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>555</v>
+        <v>547</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>556</v>
+        <v>548</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>79</v>
@@ -11980,10 +11925,10 @@
         <v>155</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>554</v>
+        <v>546</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>557</v>
+        <v>549</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>79</v>
@@ -12001,7 +11946,7 @@
         <v>79</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>552</v>
+        <v>544</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -12010,7 +11955,7 @@
         <v>91</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>159</v>
+        <v>79</v>
       </c>
       <c r="AJ81" t="s" s="2">
         <v>103</v>
@@ -12019,27 +11964,27 @@
         <v>79</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>558</v>
+        <v>550</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>559</v>
+        <v>551</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>550</v>
+        <v>542</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>551</v>
+        <v>543</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>560</v>
+        <v>552</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>561</v>
+        <v>553</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>561</v>
+        <v>553</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12065,16 +12010,16 @@
         <v>151</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>562</v>
+        <v>554</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>563</v>
+        <v>555</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>564</v>
+        <v>556</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>565</v>
+        <v>557</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>79</v>
@@ -12123,7 +12068,7 @@
         <v>79</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>561</v>
+        <v>553</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12132,7 +12077,7 @@
         <v>81</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>159</v>
+        <v>79</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>103</v>
@@ -12141,13 +12086,13 @@
         <v>79</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>566</v>
+        <v>558</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>567</v>
+        <v>559</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>550</v>
+        <v>542</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>79</v>
@@ -12158,10 +12103,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>568</v>
+        <v>560</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>568</v>
+        <v>560</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12187,16 +12132,16 @@
         <v>105</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>570</v>
+        <v>562</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>571</v>
+        <v>563</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>572</v>
+        <v>564</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>79</v>
@@ -12245,7 +12190,7 @@
         <v>79</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>568</v>
+        <v>560</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12254,7 +12199,7 @@
         <v>91</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>573</v>
+        <v>565</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>103</v>
@@ -12263,16 +12208,16 @@
         <v>79</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>574</v>
+        <v>566</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>575</v>
+        <v>567</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>550</v>
+        <v>542</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>79</v>
@@ -12280,10 +12225,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>577</v>
+        <v>569</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>577</v>
+        <v>569</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12309,16 +12254,14 @@
         <v>105</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>578</v>
+        <v>570</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>245</v>
-      </c>
+        <v>571</v>
+      </c>
+      <c r="N84" s="2"/>
       <c r="O84" t="s" s="2">
-        <v>572</v>
+        <v>564</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>79</v>
@@ -12367,7 +12310,7 @@
         <v>79</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>577</v>
+        <v>569</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12385,13 +12328,13 @@
         <v>79</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>580</v>
+        <v>572</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>550</v>
+        <v>542</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>79</v>
@@ -12402,10 +12345,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>582</v>
+        <v>574</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>582</v>
+        <v>574</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12428,19 +12371,19 @@
         <v>92</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>583</v>
+        <v>575</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>584</v>
+        <v>576</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>585</v>
+        <v>577</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>586</v>
+        <v>578</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>587</v>
+        <v>579</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>79</v>
@@ -12489,7 +12432,7 @@
         <v>79</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>582</v>
+        <v>574</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12498,7 +12441,7 @@
         <v>91</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>573</v>
+        <v>565</v>
       </c>
       <c r="AJ85" t="s" s="2">
         <v>103</v>
@@ -12507,13 +12450,13 @@
         <v>79</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>588</v>
+        <v>580</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>589</v>
+        <v>581</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>550</v>
+        <v>542</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>79</v>
@@ -12524,10 +12467,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>590</v>
+        <v>582</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>590</v>
+        <v>582</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12550,17 +12493,17 @@
         <v>79</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>591</v>
+        <v>583</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>592</v>
+        <v>584</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" t="s" s="2">
-        <v>593</v>
+        <v>585</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>79</v>
@@ -12609,7 +12552,7 @@
         <v>79</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>590</v>
+        <v>582</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12618,7 +12561,7 @@
         <v>81</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>159</v>
+        <v>79</v>
       </c>
       <c r="AJ86" t="s" s="2">
         <v>103</v>
@@ -12627,13 +12570,13 @@
         <v>79</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>595</v>
+        <v>587</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>550</v>
+        <v>542</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>79</v>
@@ -12644,10 +12587,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>596</v>
+        <v>588</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>596</v>
+        <v>588</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12762,10 +12705,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>597</v>
+        <v>589</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>597</v>
+        <v>589</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12835,16 +12778,16 @@
         <v>79</v>
       </c>
       <c r="AB88" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AC88" t="s" s="2">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="AD88" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE88" t="s" s="2">
-        <v>118</v>
+        <v>79</v>
       </c>
       <c r="AF88" t="s" s="2">
         <v>119</v>
@@ -12882,14 +12825,14 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>598</v>
+        <v>590</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>598</v>
+        <v>590</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -12911,16 +12854,16 @@
         <v>112</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="N89" t="s" s="2">
         <v>115</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>79</v>
@@ -12969,7 +12912,7 @@
         <v>79</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -12987,7 +12930,7 @@
         <v>79</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>79</v>
@@ -13004,10 +12947,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>599</v>
+        <v>591</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>599</v>
+        <v>591</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13033,14 +12976,12 @@
         <v>105</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>600</v>
+        <v>592</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>245</v>
-      </c>
+        <v>593</v>
+      </c>
+      <c r="N90" s="2"/>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>79</v>
@@ -13089,7 +13030,7 @@
         <v>79</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>599</v>
+        <v>591</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>91</v>
@@ -13107,13 +13048,13 @@
         <v>79</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>509</v>
+        <v>501</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>602</v>
+        <v>594</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>550</v>
+        <v>542</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>79</v>
@@ -13124,10 +13065,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>603</v>
+        <v>595</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>603</v>
+        <v>595</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13150,19 +13091,19 @@
         <v>79</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>604</v>
+        <v>596</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>607</v>
+        <v>599</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>608</v>
+        <v>600</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>79</v>
@@ -13211,7 +13152,7 @@
         <v>79</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>603</v>
+        <v>595</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>91</v>
@@ -13220,7 +13161,7 @@
         <v>91</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>159</v>
+        <v>79</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>103</v>
@@ -13229,13 +13170,13 @@
         <v>79</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>550</v>
+        <v>542</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>79</v>
